--- a/Shiny/Datos limpios/pricing_semanal_historico_girasol.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico_girasol.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M569"/>
+  <dimension ref="A1:M572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -24820,33 +24820,162 @@
         <v>45957</v>
       </c>
       <c r="D569">
-        <v>950</v>
+        <v>61007.96</v>
       </c>
       <c r="E569">
-        <v>0</v>
+        <v>156.9</v>
       </c>
       <c r="F569">
-        <v>0</v>
+        <v>4468</v>
       </c>
       <c r="G569">
-        <v>950</v>
+        <v>56696.86</v>
       </c>
       <c r="H569">
-        <v>0</v>
+        <v>2923.7</v>
       </c>
       <c r="I569">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J569">
         <v>0</v>
       </c>
       <c r="K569">
-        <v>0</v>
+        <v>2964.7</v>
       </c>
       <c r="L569">
-        <v>950</v>
+        <v>59661.56</v>
       </c>
       <c r="M569" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570">
+        <v>2025</v>
+      </c>
+      <c r="B570">
+        <v>45</v>
+      </c>
+      <c r="C570" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D570">
+        <v>76497.28999999999</v>
+      </c>
+      <c r="E570">
+        <v>500</v>
+      </c>
+      <c r="F570">
+        <v>14801.62</v>
+      </c>
+      <c r="G570">
+        <v>62195.66999999999</v>
+      </c>
+      <c r="H570">
+        <v>3714.43</v>
+      </c>
+      <c r="I570">
+        <v>0</v>
+      </c>
+      <c r="J570">
+        <v>0</v>
+      </c>
+      <c r="K570">
+        <v>3714.43</v>
+      </c>
+      <c r="L570">
+        <v>65910.09999999999</v>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571">
+        <v>2025</v>
+      </c>
+      <c r="B571">
+        <v>46</v>
+      </c>
+      <c r="C571" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D571">
+        <v>53805.21</v>
+      </c>
+      <c r="E571">
+        <v>1950</v>
+      </c>
+      <c r="F571">
+        <v>1526.69</v>
+      </c>
+      <c r="G571">
+        <v>54228.52</v>
+      </c>
+      <c r="H571">
+        <v>2508.39</v>
+      </c>
+      <c r="I571">
+        <v>0</v>
+      </c>
+      <c r="J571">
+        <v>0</v>
+      </c>
+      <c r="K571">
+        <v>2508.39</v>
+      </c>
+      <c r="L571">
+        <v>56736.91</v>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572">
+        <v>2025</v>
+      </c>
+      <c r="B572">
+        <v>47</v>
+      </c>
+      <c r="C572" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D572">
+        <v>42165.97</v>
+      </c>
+      <c r="E572">
+        <v>755</v>
+      </c>
+      <c r="F572">
+        <v>1112</v>
+      </c>
+      <c r="G572">
+        <v>41808.97</v>
+      </c>
+      <c r="H572">
+        <v>1586.31</v>
+      </c>
+      <c r="I572">
+        <v>0</v>
+      </c>
+      <c r="J572">
+        <v>0</v>
+      </c>
+      <c r="K572">
+        <v>1586.31</v>
+      </c>
+      <c r="L572">
+        <v>43395.28</v>
+      </c>
+      <c r="M572" t="inlineStr">
         <is>
           <t>GIRASOL</t>
         </is>
